--- a/data/trending_integrated_20261006_10.xlsx
+++ b/data/trending_integrated_20261006_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>46768822770</v>
+        <v>46823451760</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집 및 유증 물량 소화 완료 후 HLB제약 주가 급등. 리보세라닙 미국 승인 신청.</t>
+          <t>기타법인의 350만주 자사주 매집과 유증 물량 소화 언급. HLB 최초 유증 성공 및 리보세라닙 미국 승인 신청에 대한 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['자사주', '유증', '리보세라닙']</t>
+          <t>['자사주 매집', '유증', '리보세라닙']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48150</v>
+        <v>47700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.04%</t>
+          <t>'+17.92%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="F3" t="n">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="G3" t="n">
-        <v>1933</v>
+        <v>2120</v>
       </c>
       <c r="H3" t="n">
         <v>14.1</v>
@@ -702,7 +702,7 @@
         <v>14.11</v>
       </c>
       <c r="O3" t="n">
-        <v>187595116525</v>
+        <v>194376747925</v>
       </c>
       <c r="P3" t="n">
         <v>69200</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>AI 기반 FDA 문서 및 VAI 결과에 따른 HLB 주가 급등 기대. 100만원 목표.</t>
+          <t>HLB의 '꿈의 간암 신약' FDA 허가에 대한 기대감이 고조. AI 답변 및 FDA 문서 확실성 언급, MSCI 편입 가능성 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['FDA', 'VAI', '승인']</t>
+          <t>['FDA 허가', '신약', 'MSCI']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20400</v>
+        <v>4990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.57%</t>
+          <t>'+13.41%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.21</v>
+        <v>0.38</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>18790</v>
+        <v>4400</v>
       </c>
       <c r="K4" t="n">
-        <v>21400</v>
+        <v>4435</v>
       </c>
       <c r="L4" t="n">
-        <v>22300</v>
+        <v>5130</v>
       </c>
       <c r="M4" t="n">
-        <v>20250</v>
+        <v>4305</v>
       </c>
       <c r="N4" t="n">
-        <v>0.83</v>
+        <v>1.02</v>
       </c>
       <c r="O4" t="n">
-        <v>106061185265</v>
+        <v>96043225461</v>
       </c>
       <c r="P4" t="n">
-        <v>30550</v>
+        <v>8100</v>
       </c>
       <c r="Q4" t="n">
-        <v>6100</v>
+        <v>592</v>
       </c>
       <c r="R4" t="n">
-        <v>-22000</v>
+        <v>1682000</v>
       </c>
       <c r="S4" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>보안주로서의 엑스게이트, 금융고객사 다수 보유 및 대통령 점검 지시에 따른 상승 기대.</t>
+          <t>외국인 매수세 유입과 함께 4.60% 상승한 루멘텀, 12.16% 상승한 어플라이드옵토 등 관련주 상승 영향. 2일간 40% 상승 시 투경 재지정 필요 없다는 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['보안주', '금융고객사', '상승']</t>
+          <t>['외국인 매수', '투기과열종목', '상한가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18600</v>
+        <v>20550</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.49%</t>
+          <t>'+9.37%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="E5" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>358</v>
+        <v>152</v>
       </c>
       <c r="H5" t="n">
-        <v>3.81</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>17800</v>
+        <v>18790</v>
       </c>
       <c r="K5" t="n">
-        <v>18040</v>
+        <v>21400</v>
       </c>
       <c r="L5" t="n">
-        <v>18880</v>
+        <v>22300</v>
       </c>
       <c r="M5" t="n">
-        <v>17950</v>
+        <v>20200</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>0.83</v>
       </c>
       <c r="O5" t="n">
-        <v>150097202270</v>
+        <v>109197105665</v>
       </c>
       <c r="P5" t="n">
-        <v>31500</v>
+        <v>30550</v>
       </c>
       <c r="Q5" t="n">
-        <v>1272</v>
+        <v>6100</v>
       </c>
       <c r="R5" t="n">
-        <v>533000</v>
+        <v>-22000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 증시 광통신 섹터 강세 및 대한광통신 매수 기회 포착. 공매도 우려 속 2만 돌파 기대.</t>
+          <t>대통령의 보안 점검 지시와 맞물려 보안주 상승 기대감. 금융 고객사 207곳 보유 및 PC 보안, 안랩 등 타 보안주 동반 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '매수', '공매도']</t>
+          <t>['보안주', '고객사', '동반 상승']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,86 +924,86 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>277000</v>
+        <v>18590</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.36%</t>
+          <t>'+4.44%</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G6" t="n">
+        <v>378</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>17800</v>
+      </c>
+      <c r="K6" t="n">
+        <v>18040</v>
+      </c>
+      <c r="L6" t="n">
+        <v>18880</v>
+      </c>
+      <c r="M6" t="n">
+        <v>17950</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>154677439000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R6" t="n">
+        <v>533000</v>
+      </c>
+      <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="n">
-        <v>456</v>
-      </c>
-      <c r="F6" t="n">
-        <v>295</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1975</v>
-      </c>
-      <c r="H6" t="n">
-        <v>46.41</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>276000</v>
-      </c>
-      <c r="K6" t="n">
-        <v>278500</v>
-      </c>
-      <c r="L6" t="n">
-        <v>279000</v>
-      </c>
-      <c r="M6" t="n">
-        <v>275000</v>
-      </c>
-      <c r="N6" t="n">
-        <v>46.41</v>
-      </c>
-      <c r="O6" t="n">
-        <v>927223991750</v>
-      </c>
-      <c r="P6" t="n">
-        <v>374500</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>90200</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-510000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>285000</v>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>반도체 시장 폭등 랠리 및 엔비디아 신고가 경신에 따른 삼성전자 주가 상승 기대.</t>
+          <t>미국 증시의 광통신 섹터 강세와 루멘텀, 어플라이드옵토 등의 상승이 대한광통신에 대한 기대감으로 작용. 2만 돌파 목표 및 매물 소화 과정 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체', '엔비디아', '영업이익']</t>
+          <t>['광통신', '섹터', '매물 소화']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1805000</v>
+        <v>277000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.96%</t>
+          <t>'+0.36%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>535</v>
+        <v>479</v>
       </c>
       <c r="F7" t="n">
-        <v>339</v>
+        <v>305</v>
       </c>
       <c r="G7" t="n">
-        <v>1543</v>
+        <v>2029</v>
       </c>
       <c r="H7" t="n">
-        <v>49.76</v>
+        <v>46.41</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1841000</v>
+        <v>276000</v>
       </c>
       <c r="K7" t="n">
-        <v>1835000</v>
+        <v>278500</v>
       </c>
       <c r="L7" t="n">
-        <v>1837000</v>
+        <v>279000</v>
       </c>
       <c r="M7" t="n">
-        <v>1801000</v>
+        <v>275000</v>
       </c>
       <c r="N7" t="n">
-        <v>49.77</v>
+        <v>46.41</v>
       </c>
       <c r="O7" t="n">
-        <v>1228782952000</v>
+        <v>998761386250</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R7" t="n">
-        <v>-192000</v>
+        <v>-510000</v>
       </c>
       <c r="S7" t="n">
-        <v>19000</v>
+        <v>285000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>엔비디아 신고가 경신 및 AI 열풍에 따른 SK하이닉스 주가 상승 기대. 메모리 부족 전망.</t>
+          <t>반도체 시장 폭등 랠리 및 엔비디아 신고가 경신에 따른 삼성전자 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['엔비디아', 'AI', '메모리']</t>
+          <t>['반도체', '엔비디아', '영업이익']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1107,6 +1107,98 @@
         </is>
       </c>
       <c r="Z7" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1801000</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-2.17%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E8" t="n">
+        <v>574</v>
+      </c>
+      <c r="F8" t="n">
+        <v>360</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1666</v>
+      </c>
+      <c r="H8" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1841000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1835000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1837000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1801000</v>
+      </c>
+      <c r="N8" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1341331835500</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-192000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>엔비디아, TSMC 등 관련주 신고가 경신과 미국 증시 강세에 따른 SK하이닉스의 상승 기대감. 2028년까지 100% shortage 전망 언급.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['엔비디아', '반도체', '신고가']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20261006_10.xlsx
+++ b/data/trending_integrated_20261006_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13010</v>
+        <v>12880</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+29.97%</t>
+          <t>'+28.67%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G2" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>46823451760</v>
+        <v>50308462520</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>기타법인의 350만주 자사주 매집과 유증 물량 소화 언급. HLB 최초 유증 성공 및 리보세라닙 미국 승인 신청에 대한 기대감.</t>
+          <t>HLB 리보세라닙 미국 승인 신청 및 기타법인 자사주 매집에 따른 급등.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['자사주 매집', '유증', '리보세라닙']</t>
+          <t>['리보세라닙', '자사주매집', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47700</v>
+        <v>47050</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.92%</t>
+          <t>'+16.32%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="F3" t="n">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="G3" t="n">
-        <v>2120</v>
+        <v>2255</v>
       </c>
       <c r="H3" t="n">
         <v>14.1</v>
@@ -702,7 +702,7 @@
         <v>14.11</v>
       </c>
       <c r="O3" t="n">
-        <v>194376747925</v>
+        <v>197993419750</v>
       </c>
       <c r="P3" t="n">
         <v>69200</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>HLB의 '꿈의 간암 신약' FDA 허가에 대한 기대감이 고조. AI 답변 및 FDA 문서 확실성 언급, MSCI 편입 가능성 제시.</t>
+          <t>미국 FDA 간암 신약 승인 확정 및 MSCI 편입 기대감으로 인한 급등.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['FDA 허가', '신약', 'MSCI']</t>
+          <t>['FDA승인', 'MSCI편입', '간암신약']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4990</v>
+        <v>4967</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.41%</t>
+          <t>'+12.89%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.38</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H4" t="n">
         <v>1.4</v>
@@ -794,7 +794,7 @@
         <v>1.02</v>
       </c>
       <c r="O4" t="n">
-        <v>96043225461</v>
+        <v>99452952222</v>
       </c>
       <c r="P4" t="n">
         <v>8100</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외국인 매수세 유입과 함께 4.60% 상승한 루멘텀, 12.16% 상승한 어플라이드옵토 등 관련주 상승 영향. 2일간 40% 상승 시 투경 재지정 필요 없다는 언급.</t>
+          <t>외인 매수세 유입에 따른 단기 급등 및 추가 상승 기대감. 프로그램 매매 강세.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['외국인 매수', '투기과열종목', '상한가']</t>
+          <t>['외인매수', '프로그램매매', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>0.21</v>
       </c>
       <c r="E5" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H5" t="n">
         <v>1.04</v>
@@ -886,7 +886,7 @@
         <v>0.83</v>
       </c>
       <c r="O5" t="n">
-        <v>109197105665</v>
+        <v>112198452390</v>
       </c>
       <c r="P5" t="n">
         <v>30550</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대통령의 보안 점검 지시와 맞물려 보안주 상승 기대감. 금융 고객사 207곳 보유 및 PC 보안, 안랩 등 타 보안주 동반 상승 가능성 언급.</t>
+          <t>대통령 지시 관련 보안주 테마 상승 기대감. 금융고객사 기반 성장 가능성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안주', '고객사', '동반 상승']</t>
+          <t>['보안주', '대통령지시', '금융고객사']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18590</v>
+        <v>3055</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.44%</t>
+          <t>'+7.38%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.31</v>
+        <v>0.57</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>378</v>
+        <v>87</v>
       </c>
       <c r="H6" t="n">
-        <v>3.81</v>
+        <v>1.82</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>17800</v>
+        <v>2845</v>
       </c>
       <c r="K6" t="n">
-        <v>18040</v>
+        <v>3200</v>
       </c>
       <c r="L6" t="n">
-        <v>18880</v>
+        <v>3360</v>
       </c>
       <c r="M6" t="n">
-        <v>17950</v>
+        <v>2995</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>154677439000</v>
+        <v>32259855147</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>4810</v>
       </c>
       <c r="Q6" t="n">
-        <v>1272</v>
+        <v>1400</v>
       </c>
       <c r="R6" t="n">
-        <v>533000</v>
+        <v>-62000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 증시의 광통신 섹터 강세와 루멘텀, 어플라이드옵토 등의 상승이 대한광통신에 대한 기대감으로 작용. 2만 돌파 목표 및 매물 소화 과정 언급.</t>
+          <t>보안주 테마 내 개별 종목 부진 및 차익실현 매물 출회. CB 발행 부담.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '섹터', '매물 소화']</t>
+          <t>['보안주', 'CB', '차익실현']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>277000</v>
+        <v>18450</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.36%</t>
+          <t>'+3.65%</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E7" t="n">
+        <v>63</v>
+      </c>
+      <c r="F7" t="n">
+        <v>47</v>
+      </c>
+      <c r="G7" t="n">
+        <v>396</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>17800</v>
+      </c>
+      <c r="K7" t="n">
+        <v>18040</v>
+      </c>
+      <c r="L7" t="n">
+        <v>18880</v>
+      </c>
+      <c r="M7" t="n">
+        <v>17950</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>161591880080</v>
+      </c>
+      <c r="P7" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R7" t="n">
+        <v>533000</v>
+      </c>
+      <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>479</v>
-      </c>
-      <c r="F7" t="n">
-        <v>305</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2029</v>
-      </c>
-      <c r="H7" t="n">
-        <v>46.41</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>276000</v>
-      </c>
-      <c r="K7" t="n">
-        <v>278500</v>
-      </c>
-      <c r="L7" t="n">
-        <v>279000</v>
-      </c>
-      <c r="M7" t="n">
-        <v>275000</v>
-      </c>
-      <c r="N7" t="n">
-        <v>46.41</v>
-      </c>
-      <c r="O7" t="n">
-        <v>998761386250</v>
-      </c>
-      <c r="P7" t="n">
-        <v>374500</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>90200</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-510000</v>
-      </c>
-      <c r="S7" t="n">
-        <v>285000</v>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>반도체 시장 폭등 랠리 및 엔비디아 신고가 경신에 따른 삼성전자 주가 상승 기대.</t>
+          <t>미국 증시의 광통신 섹터 강세와 루멘텀, 어플라이드옵토 등의 상승이 대한광통신에 대한 기대감으로 작용. 2만 돌파 목표 및 매물 소화 과정 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['반도체', '엔비디아', '영업이익']</t>
+          <t>['광통신', '섹터', '매물 소화']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1801000</v>
+        <v>275750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.17%</t>
+          <t>'-0.09%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>574</v>
+        <v>506</v>
       </c>
       <c r="F8" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="G8" t="n">
-        <v>1666</v>
+        <v>2040</v>
       </c>
       <c r="H8" t="n">
-        <v>49.76</v>
+        <v>46.41</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1841000</v>
+        <v>276000</v>
       </c>
       <c r="K8" t="n">
-        <v>1835000</v>
+        <v>278500</v>
       </c>
       <c r="L8" t="n">
-        <v>1837000</v>
+        <v>279000</v>
       </c>
       <c r="M8" t="n">
-        <v>1801000</v>
+        <v>275000</v>
       </c>
       <c r="N8" t="n">
-        <v>49.77</v>
+        <v>46.41</v>
       </c>
       <c r="O8" t="n">
-        <v>1341331835500</v>
+        <v>1086125866500</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R8" t="n">
-        <v>-192000</v>
+        <v>-510000</v>
       </c>
       <c r="S8" t="n">
-        <v>19000</v>
+        <v>285000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>엔비디아, TSMC 등 관련주 신고가 경신과 미국 증시 강세에 따른 SK하이닉스의 상승 기대감. 2028년까지 100% shortage 전망 언급.</t>
+          <t>반도체 시장 폭등 랠리 및 엔비디아 신고가 경신에 따른 삼성전자 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['엔비디아', '반도체', '신고가']</t>
+          <t>['반도체', '엔비디아', '영업이익']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1199,6 +1199,98 @@
         </is>
       </c>
       <c r="Z8" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1798000</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-2.34%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E9" t="n">
+        <v>647</v>
+      </c>
+      <c r="F9" t="n">
+        <v>399</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1816</v>
+      </c>
+      <c r="H9" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1841000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1835000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1837000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1794000</v>
+      </c>
+      <c r="N9" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1514370075000</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-192000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>19000</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>엔비디아, TSMC 등 관련주 신고가 경신과 미국 증시 강세에 따른 SK하이닉스의 상승 기대감. 2028년까지 100% shortage 전망 언급.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['엔비디아', '반도체', '신고가']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20261006_10.xlsx
+++ b/data/trending_integrated_20261006_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12880</v>
+        <v>13010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+28.67%</t>
+          <t>'+29.97%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F2" t="n">
         <v>46</v>
       </c>
       <c r="G2" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>50308462520</v>
+        <v>52508521350</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HLB 리보세라닙 미국 승인 신청 및 기타법인 자사주 매집에 따른 급등.</t>
+          <t>기타법인 자사주 매집 및 유증 물량 소화. 리보세라닙 미국 승인 신청 관련 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['리보세라닙', '자사주매집', '급등']</t>
+          <t>['자사주매집', '유증', '리보세라닙']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47050</v>
+        <v>47800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.32%</t>
+          <t>'+18.17%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="F3" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="G3" t="n">
-        <v>2255</v>
+        <v>2335</v>
       </c>
       <c r="H3" t="n">
         <v>14.1</v>
@@ -702,7 +702,7 @@
         <v>14.11</v>
       </c>
       <c r="O3" t="n">
-        <v>197993419750</v>
+        <v>204565349025</v>
       </c>
       <c r="P3" t="n">
         <v>69200</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4967</v>
+        <v>4990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.89%</t>
+          <t>'+13.41%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.38</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="H4" t="n">
         <v>1.4</v>
@@ -794,7 +794,7 @@
         <v>1.02</v>
       </c>
       <c r="O4" t="n">
-        <v>99452952222</v>
+        <v>102025845671</v>
       </c>
       <c r="P4" t="n">
         <v>8100</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외인 매수세 유입에 따른 단기 급등 및 추가 상승 기대감. 프로그램 매매 강세.</t>
+          <t>해외 반도체 기업 급등에 따른 연동 기대감. 외국인 매수세 집중 및 상한가 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['외인매수', '프로그램매매', '급등']</t>
+          <t>['외국인매수', '상한가', '반도체']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20550</v>
+        <v>20450</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.37%</t>
+          <t>'+8.83%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.21</v>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H5" t="n">
         <v>1.04</v>
@@ -886,7 +886,7 @@
         <v>0.83</v>
       </c>
       <c r="O5" t="n">
-        <v>112198452390</v>
+        <v>113922664290</v>
       </c>
       <c r="P5" t="n">
         <v>30550</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대통령 지시 관련 보안주 테마 상승 기대감. 금융고객사 기반 성장 가능성.</t>
+          <t>대통령 지시로 인한 보안주 부각 및 성장 기대감. 금융권 고객사 확보 및 2~3배 상승 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안주', '대통령지시', '금융고객사']</t>
+          <t>['보안주', '성장주', '금융고객사']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3055</v>
+        <v>3075</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.38%</t>
+          <t>'+8.08%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.57</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H6" t="n">
         <v>1.82</v>
@@ -978,7 +978,7 @@
         <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>32259855147</v>
+        <v>33386121289</v>
       </c>
       <c r="P6" t="n">
         <v>4810</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>보안주 테마 내 개별 종목 부진 및 차익실현 매물 출회. CB 발행 부담.</t>
+          <t>장초반 급등 후 하락 및 외인 차익실현. CB 남발 및 공매도 증가로 인한 탈출 권유.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보안주', 'CB', '차익실현']</t>
+          <t>['차익실현', '공매도', 'CB']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18450</v>
+        <v>18480</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.65%</t>
+          <t>'+3.82%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G7" t="n">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="H7" t="n">
         <v>3.81</v>
@@ -1070,7 +1070,7 @@
         <v>3.5</v>
       </c>
       <c r="O7" t="n">
-        <v>161591880080</v>
+        <v>166829531380</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 증시의 광통신 섹터 강세와 루멘텀, 어플라이드옵토 등의 상승이 대한광통신에 대한 기대감으로 작용. 2만 돌파 목표 및 매물 소화 과정 언급.</t>
+          <t>미국 광통신 섹터 강세 및 국내 시장 주도 기대감. 매물 소화 과정 및 2만 돌파 목표.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', '섹터', '매물 소화']</t>
+          <t>['광통신', '매물소화', '주도주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>275750</v>
+        <v>17730</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.09%</t>
+          <t>'+0.68%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>506</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>320</v>
+        <v>24</v>
       </c>
       <c r="G8" t="n">
-        <v>2040</v>
+        <v>297</v>
       </c>
       <c r="H8" t="n">
-        <v>46.41</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>276000</v>
+        <v>17610</v>
       </c>
       <c r="K8" t="n">
-        <v>278500</v>
+        <v>17700</v>
       </c>
       <c r="L8" t="n">
-        <v>279000</v>
+        <v>18160</v>
       </c>
       <c r="M8" t="n">
-        <v>275000</v>
+        <v>17630</v>
       </c>
       <c r="N8" t="n">
-        <v>46.41</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>1086125866500</v>
+        <v>32885396870</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>90200</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>-510000</v>
+        <v>237000</v>
       </c>
       <c r="S8" t="n">
-        <v>285000</v>
+        <v>-5000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>반도체 시장 폭등 랠리 및 엔비디아 신고가 경신에 따른 삼성전자 주가 상승 기대.</t>
+          <t>주택 공급 확대와 원전 테마 관련 언급. 허매수 및 대차 해지 주장.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반도체', '엔비디아', '영업이익']</t>
+          <t>['주택공급', '원전테마', '허매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1798000</v>
+        <v>276000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.34%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>647</v>
+        <v>525</v>
       </c>
       <c r="F9" t="n">
-        <v>399</v>
+        <v>329</v>
       </c>
       <c r="G9" t="n">
-        <v>1816</v>
+        <v>2067</v>
       </c>
       <c r="H9" t="n">
-        <v>49.76</v>
+        <v>46.41</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1841000</v>
+        <v>276000</v>
       </c>
       <c r="K9" t="n">
-        <v>1835000</v>
+        <v>278500</v>
       </c>
       <c r="L9" t="n">
-        <v>1837000</v>
+        <v>279000</v>
       </c>
       <c r="M9" t="n">
-        <v>1794000</v>
+        <v>275000</v>
       </c>
       <c r="N9" t="n">
-        <v>49.77</v>
+        <v>46.41</v>
       </c>
       <c r="O9" t="n">
-        <v>1514370075000</v>
+        <v>1172958854000</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R9" t="n">
-        <v>-192000</v>
+        <v>-510000</v>
       </c>
       <c r="S9" t="n">
-        <v>19000</v>
+        <v>285000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>엔비디아, TSMC 등 관련주 신고가 경신과 미국 증시 강세에 따른 SK하이닉스의 상승 기대감. 2028년까지 100% shortage 전망 언급.</t>
+          <t>반도체 시장 폭등 랠리 및 엔비디아 신고가 경신에 따른 삼성전자 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['엔비디아', '반도체', '신고가']</t>
+          <t>['반도체', '엔비디아', '영업이익']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1291,6 +1291,98 @@
         </is>
       </c>
       <c r="Z9" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1804000</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-2.01%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E10" t="n">
+        <v>699</v>
+      </c>
+      <c r="F10" t="n">
+        <v>419</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1915</v>
+      </c>
+      <c r="H10" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1841000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1835000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1837000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1791000</v>
+      </c>
+      <c r="N10" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1636338297500</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-192000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>19000</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>엔비디아, TSMC 등 관련주 신고가 경신과 미국 증시 강세에 따른 SK하이닉스의 상승 기대감. 2028년까지 100% shortage 전망 언급.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['엔비디아', '반도체', '신고가']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20261006_10.xlsx
+++ b/data/trending_integrated_20261006_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52508521350</v>
+        <v>52520360450</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집 및 유증 물량 소화. 리보세라닙 미국 승인 신청 관련 기대감.</t>
+          <t>HLB와의 연관성, 기타법인 자사주 매집, 리보세라닙 미국 승인 신청 등 호재 기반 급등세. 유증 물량 소화 완료.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['자사주매집', '유증', '리보세라닙']</t>
+          <t>['유증', '리보세라닙', '자사주 매집']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47800</v>
+        <v>47525</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.17%</t>
+          <t>'+17.49%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="F3" t="n">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="G3" t="n">
-        <v>2335</v>
+        <v>2437</v>
       </c>
       <c r="H3" t="n">
         <v>14.1</v>
@@ -702,7 +702,7 @@
         <v>14.11</v>
       </c>
       <c r="O3" t="n">
-        <v>204565349025</v>
+        <v>210549079700</v>
       </c>
       <c r="P3" t="n">
         <v>69200</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 FDA 간암 신약 승인 확정 및 MSCI 편입 기대감으로 인한 급등.</t>
+          <t>FDA 승인 기대감 및 AI 답변 근거 제시. MSCI 편입을 통한 자금 유입 전망과 함께 100만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['FDA승인', 'MSCI편입', '간암신약']</t>
+          <t>['FDA 승인', 'MSCI 편입', '신약']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4990</v>
+        <v>5020</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.41%</t>
+          <t>'+14.09%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.38</v>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" t="n">
         <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="H4" t="n">
         <v>1.4</v>
@@ -794,7 +794,7 @@
         <v>1.02</v>
       </c>
       <c r="O4" t="n">
-        <v>102025845671</v>
+        <v>105922715052</v>
       </c>
       <c r="P4" t="n">
         <v>8100</v>
@@ -839,70 +839,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20450</v>
+        <v>1460</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.83%</t>
+          <t>'+8.96%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>18790</v>
+        <v>1340</v>
       </c>
       <c r="K5" t="n">
-        <v>21400</v>
+        <v>1370</v>
       </c>
       <c r="L5" t="n">
-        <v>22300</v>
+        <v>1555</v>
       </c>
       <c r="M5" t="n">
-        <v>20200</v>
+        <v>1360</v>
       </c>
       <c r="N5" t="n">
-        <v>0.83</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>113922664290</v>
+        <v>17748448351</v>
       </c>
       <c r="P5" t="n">
-        <v>30550</v>
+        <v>2970</v>
       </c>
       <c r="Q5" t="n">
-        <v>6100</v>
+        <v>890</v>
       </c>
       <c r="R5" t="n">
-        <v>-22000</v>
+        <v>-72000</v>
       </c>
       <c r="S5" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대통령 지시로 인한 보안주 부각 및 성장 기대감. 금융권 고객사 확보 및 2~3배 상승 전망.</t>
+          <t>미국 알래스카 LNG 사업 실현 언급, 송유관 건설 관련 매출 기대. 일부 투자자는 매도 성공했으나, 주가 변동성에 대한 우려도 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안주', '성장주', '금융고객사']</t>
+          <t>['LNG 사업', '송유관', '매출']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3075</v>
+        <v>20300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.08%</t>
+          <t>'+8.04%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.57</v>
+        <v>0.21</v>
       </c>
       <c r="E6" t="n">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="H6" t="n">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2845</v>
+        <v>18790</v>
       </c>
       <c r="K6" t="n">
-        <v>3200</v>
+        <v>21400</v>
       </c>
       <c r="L6" t="n">
-        <v>3360</v>
+        <v>22300</v>
       </c>
       <c r="M6" t="n">
-        <v>2995</v>
+        <v>20200</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="O6" t="n">
-        <v>33386121289</v>
+        <v>115280203240</v>
       </c>
       <c r="P6" t="n">
-        <v>4810</v>
+        <v>30550</v>
       </c>
       <c r="Q6" t="n">
-        <v>1400</v>
+        <v>6100</v>
       </c>
       <c r="R6" t="n">
-        <v>-62000</v>
+        <v>-22000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>장초반 급등 후 하락 및 외인 차익실현. CB 남발 및 공매도 증가로 인한 탈출 권유.</t>
+          <t>대통령 지시로 인한 보안주 부각 및 성장 기대감. 금융권 고객사 확보 및 2~3배 상승 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['차익실현', '공매도', 'CB']</t>
+          <t>['보안주', '성장주', '금융고객사']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18480</v>
+        <v>3045</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.82%</t>
+          <t>'+7.03%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.31</v>
+        <v>0.57</v>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n">
-        <v>407</v>
+        <v>113</v>
       </c>
       <c r="H7" t="n">
-        <v>3.81</v>
+        <v>1.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>17800</v>
+        <v>2845</v>
       </c>
       <c r="K7" t="n">
-        <v>18040</v>
+        <v>3200</v>
       </c>
       <c r="L7" t="n">
-        <v>18880</v>
+        <v>3360</v>
       </c>
       <c r="M7" t="n">
-        <v>17950</v>
+        <v>2995</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>166829531380</v>
+        <v>33840545885</v>
       </c>
       <c r="P7" t="n">
-        <v>31500</v>
+        <v>4810</v>
       </c>
       <c r="Q7" t="n">
-        <v>1272</v>
+        <v>1400</v>
       </c>
       <c r="R7" t="n">
-        <v>533000</v>
+        <v>-62000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세 및 국내 시장 주도 기대감. 매물 소화 과정 및 2만 돌파 목표.</t>
+          <t>개별 종목의 주가 부진 및 투자자 이탈 심리. CB 남발 및 공매도 증가 우려, 타 보안주 이동 권유.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', '매물소화', '주도주']</t>
+          <t>['CB', '공매도', '주가 부진']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,86 +1108,86 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17730</v>
+        <v>18520</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.68%</t>
+          <t>'+4.04%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.06</v>
+        <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G8" t="n">
-        <v>297</v>
+        <v>433</v>
       </c>
       <c r="H8" t="n">
-        <v>9.390000000000001</v>
+        <v>3.81</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>17610</v>
+        <v>17800</v>
       </c>
       <c r="K8" t="n">
-        <v>17700</v>
+        <v>18040</v>
       </c>
       <c r="L8" t="n">
-        <v>18160</v>
+        <v>18880</v>
       </c>
       <c r="M8" t="n">
-        <v>17630</v>
+        <v>17950</v>
       </c>
       <c r="N8" t="n">
-        <v>9.449999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
-        <v>32885396870</v>
+        <v>170517378570</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>1272</v>
       </c>
       <c r="R8" t="n">
-        <v>237000</v>
+        <v>533000</v>
       </c>
       <c r="S8" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>주택 공급 확대와 원전 테마 관련 언급. 허매수 및 대차 해지 주장.</t>
+          <t>미국 증시 광통신 섹터 강세 및 국내 관련주 동반 상승 기대. 매물대 소화 과정 언급하며 상승 흐름 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주택공급', '원전테마', '허매도']</t>
+          <t>['광통신', '매물 소화', '상승 흐름']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>276000</v>
+        <v>17750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.80%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>525</v>
+        <v>41</v>
       </c>
       <c r="F9" t="n">
-        <v>329</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>2067</v>
+        <v>304</v>
       </c>
       <c r="H9" t="n">
-        <v>46.41</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>276000</v>
+        <v>17610</v>
       </c>
       <c r="K9" t="n">
-        <v>278500</v>
+        <v>17700</v>
       </c>
       <c r="L9" t="n">
-        <v>279000</v>
+        <v>18160</v>
       </c>
       <c r="M9" t="n">
-        <v>275000</v>
+        <v>17630</v>
       </c>
       <c r="N9" t="n">
-        <v>46.41</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>1172958854000</v>
+        <v>34015354215</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>90200</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>-510000</v>
+        <v>237000</v>
       </c>
       <c r="S9" t="n">
-        <v>285000</v>
+        <v>-5000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>반도체 시장 폭등 랠리 및 엔비디아 신고가 경신에 따른 삼성전자 주가 상승 기대.</t>
+          <t>주택 공급 확대 및 건설 테마 기대감에도 불구하고, 주가 하락 및 시장 조작 의혹 제기. 대주주 변경 이슈 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '엔비디아', '영업이익']</t>
+          <t>['주택 공급', '건설 테마', '주가 조작']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1804000</v>
+        <v>275250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.01%</t>
+          <t>'-0.27%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>699</v>
+        <v>549</v>
       </c>
       <c r="F10" t="n">
-        <v>419</v>
+        <v>339</v>
       </c>
       <c r="G10" t="n">
-        <v>1915</v>
+        <v>2145</v>
       </c>
       <c r="H10" t="n">
-        <v>49.76</v>
+        <v>46.41</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1841000</v>
+        <v>276000</v>
       </c>
       <c r="K10" t="n">
-        <v>1835000</v>
+        <v>278500</v>
       </c>
       <c r="L10" t="n">
-        <v>1837000</v>
+        <v>279000</v>
       </c>
       <c r="M10" t="n">
-        <v>1791000</v>
+        <v>275000</v>
       </c>
       <c r="N10" t="n">
-        <v>49.77</v>
+        <v>46.41</v>
       </c>
       <c r="O10" t="n">
-        <v>1636338297500</v>
+        <v>1234168747750</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R10" t="n">
-        <v>-192000</v>
+        <v>-510000</v>
       </c>
       <c r="S10" t="n">
-        <v>19000</v>
+        <v>285000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>엔비디아, TSMC 등 관련주 신고가 경신과 미국 증시 강세에 따른 SK하이닉스의 상승 기대감. 2028년까지 100% shortage 전망 언급.</t>
+          <t>반도체 시장 랠리 및 외국인 수급 기대감 속 3분기 영업이익 전망. 일부 정치적 언급 및 타사 주가 비교 내용 포함.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['엔비디아', '반도체', '신고가']</t>
+          <t>['반도체', '영업이익', '외국인 수급']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1383,6 +1383,98 @@
         </is>
       </c>
       <c r="Z10" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1798000</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-2.34%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E11" t="n">
+        <v>732</v>
+      </c>
+      <c r="F11" t="n">
+        <v>436</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H11" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1841000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1835000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1837000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1791000</v>
+      </c>
+      <c r="N11" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1717037427000</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-192000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>19000</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>미국 증시 및 엔비디아 강세와 연동한 상승 기대감. 다만, 메모리 반도체 시장 부진 및 국내 증시 악재 언급.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['메모리 반도체', '엔비디아', '미국 증시']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20261006_10.xlsx
+++ b/data/trending_integrated_20261006_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52520360450</v>
+        <v>52534177070</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HLB와의 연관성, 기타법인 자사주 매집, 리보세라닙 미국 승인 신청 등 호재 기반 급등세. 유증 물량 소화 완료.</t>
+          <t>HLB의 간암 신약 미국 승인 신청 및 기타법인 대규모 자사주 매집으로 인한 2연상 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['유증', '리보세라닙', '자사주 매집']</t>
+          <t>['리보세라닙', '유증', '자사주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47525</v>
+        <v>47800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.49%</t>
+          <t>'+18.17%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>504</v>
+        <v>521</v>
       </c>
       <c r="F3" t="n">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="G3" t="n">
-        <v>2437</v>
+        <v>2596</v>
       </c>
       <c r="H3" t="n">
         <v>14.1</v>
@@ -702,7 +702,7 @@
         <v>14.11</v>
       </c>
       <c r="O3" t="n">
-        <v>210549079700</v>
+        <v>212628036800</v>
       </c>
       <c r="P3" t="n">
         <v>69200</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>FDA 승인 기대감 및 AI 답변 근거 제시. MSCI 편입을 통한 자금 유입 전망과 함께 100만원 목표가 제시.</t>
+          <t>미국 FDA 간암 신약 승인 기대감 및 MSCI 편입 가능성으로 인한 폭등 가능성 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['FDA 승인', 'MSCI 편입', '신약']</t>
+          <t>['간암 신약', 'FDA', 'MSCI']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5020</v>
+        <v>17560</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.09%</t>
+          <t>'+14.32%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4</v>
+        <v>2.17</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>4400</v>
+        <v>15360</v>
       </c>
       <c r="K4" t="n">
-        <v>4435</v>
+        <v>18000</v>
       </c>
       <c r="L4" t="n">
-        <v>5130</v>
+        <v>18500</v>
       </c>
       <c r="M4" t="n">
-        <v>4305</v>
+        <v>16800</v>
       </c>
       <c r="N4" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="O4" t="n">
-        <v>105922715052</v>
+        <v>62734270600</v>
       </c>
       <c r="P4" t="n">
-        <v>8100</v>
+        <v>38400</v>
       </c>
       <c r="Q4" t="n">
-        <v>592</v>
+        <v>8010</v>
       </c>
       <c r="R4" t="n">
-        <v>1682000</v>
+        <v>-18000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>해외 반도체 기업 급등에 따른 연동 기대감. 외국인 매수세 집중 및 상한가 기대.</t>
+          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['외국인매수', '상한가', '반도체']</t>
+          <t>['AI 보안', '대장주', '테마']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>488280</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1460</v>
+        <v>5010</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.96%</t>
+          <t>'+13.86%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.17</v>
+        <v>0.38</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="H5" t="n">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1340</v>
+        <v>4400</v>
       </c>
       <c r="K5" t="n">
-        <v>1370</v>
+        <v>4435</v>
       </c>
       <c r="L5" t="n">
-        <v>1555</v>
+        <v>5130</v>
       </c>
       <c r="M5" t="n">
-        <v>1360</v>
+        <v>4305</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>17748448351</v>
+        <v>107655286755</v>
       </c>
       <c r="P5" t="n">
-        <v>2970</v>
+        <v>8100</v>
       </c>
       <c r="Q5" t="n">
-        <v>890</v>
+        <v>592</v>
       </c>
       <c r="R5" t="n">
-        <v>-72000</v>
+        <v>1682000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 알래스카 LNG 사업 실현 언급, 송유관 건설 관련 매출 기대. 일부 투자자는 매도 성공했으나, 주가 변동성에 대한 우려도 존재.</t>
+          <t>해외 반도체 기업 급등에 따른 연동 기대감. 외국인 매수세 집중 및 상한가 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['LNG 사업', '송유관', '매출']</t>
+          <t>['외국인매수', '상한가', '반도체']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20300</v>
+        <v>1458</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.04%</t>
+          <t>'+8.81%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="E6" t="n">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18790</v>
+        <v>1340</v>
       </c>
       <c r="K6" t="n">
-        <v>21400</v>
+        <v>1370</v>
       </c>
       <c r="L6" t="n">
-        <v>22300</v>
+        <v>1555</v>
       </c>
       <c r="M6" t="n">
-        <v>20200</v>
+        <v>1360</v>
       </c>
       <c r="N6" t="n">
-        <v>0.83</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
-        <v>115280203240</v>
+        <v>17926341563</v>
       </c>
       <c r="P6" t="n">
-        <v>30550</v>
+        <v>2970</v>
       </c>
       <c r="Q6" t="n">
-        <v>6100</v>
+        <v>890</v>
       </c>
       <c r="R6" t="n">
-        <v>-22000</v>
+        <v>-72000</v>
       </c>
       <c r="S6" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대통령 지시로 인한 보안주 부각 및 성장 기대감. 금융권 고객사 확보 및 2~3배 상승 전망.</t>
+          <t>미국 부통령의 알래스카 LNG 사업 언급 및 한국 참여 의사 표명으로 인한 송유관 관련 사업 수혜 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보안주', '성장주', '금융고객사']</t>
+          <t>['LNG', '송유관', '테마']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3045</v>
+        <v>20100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.03%</t>
+          <t>'+6.97%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.57</v>
+        <v>0.21</v>
       </c>
       <c r="E7" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="H7" t="n">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2845</v>
+        <v>18790</v>
       </c>
       <c r="K7" t="n">
-        <v>3200</v>
+        <v>21400</v>
       </c>
       <c r="L7" t="n">
-        <v>3360</v>
+        <v>22300</v>
       </c>
       <c r="M7" t="n">
-        <v>2995</v>
+        <v>20050</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="O7" t="n">
-        <v>33840545885</v>
+        <v>118131636565</v>
       </c>
       <c r="P7" t="n">
-        <v>4810</v>
+        <v>30550</v>
       </c>
       <c r="Q7" t="n">
-        <v>1400</v>
+        <v>6100</v>
       </c>
       <c r="R7" t="n">
-        <v>-62000</v>
+        <v>-22000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>개별 종목의 주가 부진 및 투자자 이탈 심리. CB 남발 및 공매도 증가 우려, 타 보안주 이동 권유.</t>
+          <t>대통령의 보안 점검 지시 및 금융권 해킹 이슈 부각으로 인한 보안주 전반의 상승 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['CB', '공매도', '주가 부진']</t>
+          <t>['보안주', '금융 해킹', 'AI']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18520</v>
+        <v>3025</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.04%</t>
+          <t>'+6.33%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.31</v>
+        <v>0.57</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="F8" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>433</v>
+        <v>121</v>
       </c>
       <c r="H8" t="n">
-        <v>3.81</v>
+        <v>1.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>17800</v>
+        <v>2845</v>
       </c>
       <c r="K8" t="n">
-        <v>18040</v>
+        <v>3200</v>
       </c>
       <c r="L8" t="n">
-        <v>18880</v>
+        <v>3360</v>
       </c>
       <c r="M8" t="n">
-        <v>17950</v>
+        <v>2995</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>170517378570</v>
+        <v>34435523275</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>4810</v>
       </c>
       <c r="Q8" t="n">
-        <v>1272</v>
+        <v>1400</v>
       </c>
       <c r="R8" t="n">
-        <v>533000</v>
+        <v>-62000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 증시 광통신 섹터 강세 및 국내 관련주 동반 상승 기대. 매물대 소화 과정 언급하며 상승 흐름 전망.</t>
+          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', '매물 소화', '상승 흐름']</t>
+          <t>['CB', '차익실현', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17750</v>
+        <v>18540</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.80%</t>
+          <t>'+4.16%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>304</v>
+        <v>452</v>
       </c>
       <c r="H9" t="n">
-        <v>9.390000000000001</v>
+        <v>3.81</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17610</v>
+        <v>17800</v>
       </c>
       <c r="K9" t="n">
-        <v>17700</v>
+        <v>18040</v>
       </c>
       <c r="L9" t="n">
-        <v>18160</v>
+        <v>18880</v>
       </c>
       <c r="M9" t="n">
-        <v>17630</v>
+        <v>17950</v>
       </c>
       <c r="N9" t="n">
-        <v>9.449999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>34015354215</v>
+        <v>173882922875</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>1272</v>
       </c>
       <c r="R9" t="n">
-        <v>237000</v>
+        <v>533000</v>
       </c>
       <c r="S9" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주택 공급 확대 및 건설 테마 기대감에도 불구하고, 주가 하락 및 시장 조작 의혹 제기. 대주주 변경 이슈 언급.</t>
+          <t>미국 증시 광통신 섹터 강세 및 국내 주식 시장 주도 흐름 속 매물 소화 후 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주택 공급', '건설 테마', '주가 조작']</t>
+          <t>['광통신', '매물 소화', '대장주']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>275250</v>
+        <v>17720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.27%</t>
+          <t>'+0.62%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>549</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
-        <v>339</v>
+        <v>26</v>
       </c>
       <c r="G10" t="n">
-        <v>2145</v>
+        <v>304</v>
       </c>
       <c r="H10" t="n">
-        <v>46.41</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>276000</v>
+        <v>17610</v>
       </c>
       <c r="K10" t="n">
-        <v>278500</v>
+        <v>17700</v>
       </c>
       <c r="L10" t="n">
-        <v>279000</v>
+        <v>18160</v>
       </c>
       <c r="M10" t="n">
-        <v>275000</v>
+        <v>17630</v>
       </c>
       <c r="N10" t="n">
-        <v>46.41</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>1234168747750</v>
+        <v>35378827925</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>90200</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-510000</v>
+        <v>237000</v>
       </c>
       <c r="S10" t="n">
-        <v>285000</v>
+        <v>-5000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>반도체 시장 랠리 및 외국인 수급 기대감 속 3분기 영업이익 전망. 일부 정치적 언급 및 타사 주가 비교 내용 포함.</t>
+          <t>주택 공급 확대 기사에도 불구하고, 원전 테마 언급 및 주가 누르기 의혹 제기로 인한 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '영업이익', '외국인 수급']</t>
+          <t>['주택 공급', '원전 테마', '허매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1798000</v>
+        <v>275500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.34%</t>
+          <t>'-0.18%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>732</v>
+        <v>585</v>
       </c>
       <c r="F11" t="n">
-        <v>436</v>
+        <v>345</v>
       </c>
       <c r="G11" t="n">
-        <v>2022</v>
+        <v>2205</v>
       </c>
       <c r="H11" t="n">
-        <v>49.76</v>
+        <v>46.41</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1841000</v>
+        <v>276000</v>
       </c>
       <c r="K11" t="n">
-        <v>1835000</v>
+        <v>278500</v>
       </c>
       <c r="L11" t="n">
-        <v>1837000</v>
+        <v>279000</v>
       </c>
       <c r="M11" t="n">
-        <v>1791000</v>
+        <v>274500</v>
       </c>
       <c r="N11" t="n">
-        <v>49.77</v>
+        <v>46.41</v>
       </c>
       <c r="O11" t="n">
-        <v>1717037427000</v>
+        <v>1327488706250</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R11" t="n">
-        <v>-192000</v>
+        <v>-510000</v>
       </c>
       <c r="S11" t="n">
-        <v>19000</v>
+        <v>285000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 증시 및 엔비디아 강세와 연동한 상승 기대감. 다만, 메모리 반도체 시장 부진 및 국내 증시 악재 언급.</t>
+          <t>반도체 시장 랠리 및 외국인 수급 기대감 속 3분기 영업이익 전망. 일부 정치적 언급 및 타사 주가 비교 내용 포함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['메모리 반도체', '엔비디아', '미국 증시']</t>
+          <t>['반도체', '영업이익', '외국인 수급']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1475,6 +1475,98 @@
         </is>
       </c>
       <c r="Z11" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1801000</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-2.17%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E12" t="n">
+        <v>757</v>
+      </c>
+      <c r="F12" t="n">
+        <v>449</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2115</v>
+      </c>
+      <c r="H12" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1841000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1835000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1837000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1791000</v>
+      </c>
+      <c r="N12" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1798060474000</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-192000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>19000</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>미국 증시 AI 열풍에도 불구하고 메모리 반도체 부진 및 솔리다임 상장 이슈로 인한 주가 약세.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['메모리 반도체', 'AI', '솔리다임']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>000660</t>
         </is>
